--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0010224B-8969-4CC7-8C1B-2F5057D18148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C67CE25-140A-4978-A4B4-8F147615DBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30870" yWindow="1905" windowWidth="21600" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32805" yWindow="2295" windowWidth="21600" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -427,9 +427,6 @@
     <t>£836.5</t>
   </si>
   <si>
-    <t>£27.76</t>
-  </si>
-  <si>
     <t>£23.13</t>
   </si>
   <si>
@@ -463,18 +460,6 @@
     <t>£93.69</t>
   </si>
   <si>
-    <t>£152.35</t>
-  </si>
-  <si>
-    <t>£146.92</t>
-  </si>
-  <si>
-    <t>£535.35</t>
-  </si>
-  <si>
-    <t>£428.28</t>
-  </si>
-  <si>
     <t>£22.39</t>
   </si>
   <si>
@@ -827,6 +812,21 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£126.96</t>
+  </si>
+  <si>
+    <t>£122.43</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
   </si>
 </sst>
 </file>
@@ -1261,19 +1261,19 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H2" t="s">
         <v>67</v>
@@ -1282,7 +1282,7 @@
         <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K2" t="s">
         <v>106</v>
@@ -1297,16 +1297,16 @@
         <v>135</v>
       </c>
       <c r="O2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="P2" t="s">
         <v>89</v>
       </c>
       <c r="Q2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="R2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
         <v>68</v>
@@ -1353,16 +1353,16 @@
         <v>136</v>
       </c>
       <c r="O3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="P3" t="s">
         <v>89</v>
       </c>
       <c r="Q3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="R3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1373,19 +1373,19 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H4" t="s">
         <v>69</v>
@@ -1409,16 +1409,16 @@
         <v>137</v>
       </c>
       <c r="O4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="P4" t="s">
         <v>89</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="R4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1429,19 +1429,19 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
@@ -1450,7 +1450,7 @@
         <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K5" t="s">
         <v>109</v>
@@ -1465,16 +1465,16 @@
         <v>138</v>
       </c>
       <c r="O5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P5" t="s">
         <v>89</v>
       </c>
       <c r="Q5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1485,19 +1485,19 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H6" t="s">
         <v>71</v>
@@ -1521,16 +1521,16 @@
         <v>139</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="P6" t="s">
         <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="R6" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1541,19 +1541,19 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H7" t="s">
         <v>72</v>
@@ -1562,7 +1562,7 @@
         <v>88</v>
       </c>
       <c r="J7" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="K7" t="s">
         <v>111</v>
@@ -1574,19 +1574,19 @@
         <v>125</v>
       </c>
       <c r="N7" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="O7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="P7" t="s">
         <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="R7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1597,19 +1597,19 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H8" t="s">
         <v>72</v>
@@ -1618,7 +1618,7 @@
         <v>89</v>
       </c>
       <c r="J8" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K8" t="s">
         <v>112</v>
@@ -1633,16 +1633,16 @@
         <v>140</v>
       </c>
       <c r="O8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="P8" t="s">
         <v>89</v>
       </c>
       <c r="Q8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="R8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1653,19 +1653,19 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
@@ -1674,7 +1674,7 @@
         <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K9" t="s">
         <v>113</v>
@@ -1689,16 +1689,16 @@
         <v>141</v>
       </c>
       <c r="O9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P9" t="s">
         <v>89</v>
       </c>
       <c r="Q9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="R9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1709,19 +1709,19 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
@@ -1742,19 +1742,19 @@
         <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="O10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P10" t="s">
         <v>89</v>
       </c>
       <c r="Q10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="R10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1765,19 +1765,19 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H11" t="s">
         <v>75</v>
@@ -1786,7 +1786,7 @@
         <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
@@ -1801,16 +1801,16 @@
         <v>142</v>
       </c>
       <c r="O11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s">
         <v>89</v>
       </c>
       <c r="Q11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="R11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1821,19 +1821,19 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E12" t="s">
         <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H12" t="s">
         <v>66</v>
@@ -1842,7 +1842,7 @@
         <v>93</v>
       </c>
       <c r="J12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K12" t="s">
         <v>66</v>
@@ -1854,16 +1854,16 @@
         <v>129</v>
       </c>
       <c r="N12" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="P12" t="s">
         <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="R12" t="s">
         <v>66</v>
@@ -1877,19 +1877,19 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H13" t="s">
         <v>76</v>
@@ -1898,7 +1898,7 @@
         <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K13" t="s">
         <v>115</v>
@@ -1910,19 +1910,19 @@
         <v>130</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O13" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P13" t="s">
         <v>89</v>
       </c>
       <c r="Q13" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="R13" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1933,19 +1933,19 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E14" t="s">
         <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G14" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H14" t="s">
         <v>77</v>
@@ -1966,16 +1966,16 @@
         <v>131</v>
       </c>
       <c r="N14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O14" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P14" t="s">
         <v>89</v>
       </c>
       <c r="Q14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="R14" t="s">
         <v>66</v>
@@ -1989,19 +1989,19 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E15" t="s">
         <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G15" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H15" t="s">
         <v>78</v>
@@ -2025,13 +2025,13 @@
         <v>145</v>
       </c>
       <c r="O15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P15" t="s">
         <v>89</v>
       </c>
       <c r="Q15" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="R15" t="s">
         <v>66</v>
@@ -2045,19 +2045,19 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G16" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H16" t="s">
         <v>79</v>
@@ -2066,7 +2066,7 @@
         <v>97</v>
       </c>
       <c r="J16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="K16" t="s">
         <v>118</v>
@@ -2078,19 +2078,19 @@
         <v>133</v>
       </c>
       <c r="N16" t="s">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="O16" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="P16" t="s">
         <v>89</v>
       </c>
       <c r="Q16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="R16" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2101,7 +2101,7 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2157,10 +2157,10 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
@@ -2169,7 +2169,7 @@
         <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H18" t="s">
         <v>66</v>
@@ -2178,7 +2178,7 @@
         <v>66</v>
       </c>
       <c r="J18" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="K18" t="s">
         <v>66</v>
@@ -2190,10 +2190,10 @@
         <v>66</v>
       </c>
       <c r="N18" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="O18" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P18" t="s">
         <v>89</v>
@@ -2202,7 +2202,7 @@
         <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2213,10 +2213,10 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
         <v>66</v>
@@ -2225,7 +2225,7 @@
         <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H19" t="s">
         <v>66</v>
@@ -2234,7 +2234,7 @@
         <v>66</v>
       </c>
       <c r="J19" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="K19" t="s">
         <v>66</v>
@@ -2246,10 +2246,10 @@
         <v>66</v>
       </c>
       <c r="N19" t="s">
-        <v>148</v>
+        <v>266</v>
       </c>
       <c r="O19" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="P19" t="s">
         <v>89</v>
@@ -2258,7 +2258,7 @@
         <v>66</v>
       </c>
       <c r="R19" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2269,10 +2269,10 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
         <v>66</v>
@@ -2325,10 +2325,10 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
@@ -2381,10 +2381,10 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
         <v>66</v>
@@ -2402,7 +2402,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="K22" t="s">
         <v>66</v>
@@ -2437,19 +2437,19 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H23" t="s">
         <v>80</v>
@@ -2461,7 +2461,7 @@
         <v>66</v>
       </c>
       <c r="K23" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s">
         <v>66</v>
@@ -2470,10 +2470,10 @@
         <v>134</v>
       </c>
       <c r="N23" t="s">
-        <v>149</v>
+        <v>267</v>
       </c>
       <c r="O23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="P23" t="s">
         <v>66</v>
@@ -2482,7 +2482,7 @@
         <v>66</v>
       </c>
       <c r="R23" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2493,19 +2493,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H24" t="s">
         <v>81</v>
@@ -2517,7 +2517,7 @@
         <v>66</v>
       </c>
       <c r="K24" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L24" t="s">
         <v>66</v>
@@ -2526,10 +2526,10 @@
         <v>89</v>
       </c>
       <c r="N24" t="s">
-        <v>149</v>
+        <v>267</v>
       </c>
       <c r="O24" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="P24" t="s">
         <v>66</v>
@@ -2538,7 +2538,7 @@
         <v>66</v>
       </c>
       <c r="R24" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2549,19 +2549,19 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F25" t="s">
         <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H25" t="s">
         <v>82</v>
@@ -2582,10 +2582,10 @@
         <v>89</v>
       </c>
       <c r="N25" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="O25" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="P25" t="s">
         <v>66</v>
@@ -2594,7 +2594,7 @@
         <v>66</v>
       </c>
       <c r="R25" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
